--- a/results/reports/year_2019_report.xlsx
+++ b/results/reports/year_2019_report.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,30 +502,40 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>top_30_return_compounded</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>top_30_excess</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>decile_return_compounded</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>decile_excess</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>OMXS30_return</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>OMXC25_return</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>OMXH25_return</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>OSEBX_return</t>
         </is>
@@ -569,15 +579,21 @@
         <v>32.22</v>
       </c>
       <c r="M2" t="n">
+        <v>30.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="O2" t="n">
         <v>24.42</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>20.55</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -676,7 +692,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6983401854998147</v>
+        <v>0.6983401854998145</v>
       </c>
       <c r="E4" t="n">
         <v>4.1867</v>
@@ -696,7 +712,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6919322411142765</v>
+        <v>0.6919322411142764</v>
       </c>
       <c r="E5" t="n">
         <v>3.1643</v>
@@ -736,7 +752,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6760614234117337</v>
+        <v>0.6760614234117338</v>
       </c>
       <c r="E7" t="n">
         <v>4.6027</v>
@@ -776,7 +792,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6680353861069678</v>
+        <v>0.6680353861069679</v>
       </c>
       <c r="E9" t="n">
         <v>8.0594</v>
@@ -796,7 +812,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6626591061120208</v>
+        <v>0.6626591061120207</v>
       </c>
       <c r="E10" t="n">
         <v>12.093</v>
@@ -836,7 +852,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6582004939662142</v>
+        <v>0.6582004939662141</v>
       </c>
       <c r="E12" t="n">
         <v>7.9106</v>
@@ -896,7 +912,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6437598958489472</v>
+        <v>0.6437598958489474</v>
       </c>
       <c r="E15" t="n">
         <v>19.4915</v>
@@ -916,7 +932,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6375441412193249</v>
+        <v>0.6375441412193248</v>
       </c>
       <c r="E16" t="n">
         <v>-1.0814</v>
@@ -996,7 +1012,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.625196608252421</v>
+        <v>0.6251966082524208</v>
       </c>
       <c r="E20" t="n">
         <v>7.5212</v>
@@ -1102,7 +1118,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7176547411822644</v>
+        <v>0.7176547411822642</v>
       </c>
       <c r="E3" t="n">
         <v>4.0361</v>
@@ -1142,7 +1158,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6939867989200422</v>
+        <v>0.6939867989200421</v>
       </c>
       <c r="E5" t="n">
         <v>-2.9211</v>
@@ -1162,7 +1178,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6883931044049938</v>
+        <v>0.6883931044049939</v>
       </c>
       <c r="E6" t="n">
         <v>-3.2609</v>
@@ -1182,7 +1198,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6767809593519547</v>
+        <v>0.6767809593519548</v>
       </c>
       <c r="E7" t="n">
         <v>3.7013</v>
@@ -1222,7 +1238,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6472379873434347</v>
+        <v>0.6472379873434346</v>
       </c>
       <c r="E9" t="n">
         <v>1.6794</v>
@@ -1282,7 +1298,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6271488533785725</v>
+        <v>0.6271488533785726</v>
       </c>
       <c r="E12" t="n">
         <v>-0.9639</v>
@@ -1422,7 +1438,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6171683759875869</v>
+        <v>0.6171683759875868</v>
       </c>
       <c r="E19" t="n">
         <v>11.9243</v>
@@ -1608,7 +1624,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.686115498058661</v>
+        <v>0.6861154980586612</v>
       </c>
       <c r="E6" t="n">
         <v>7.2283</v>
@@ -1648,7 +1664,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6684015803418903</v>
+        <v>0.6684015803418901</v>
       </c>
       <c r="E8" t="n">
         <v>1.8475</v>
@@ -1688,7 +1704,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6610898380587632</v>
+        <v>0.6610898380587631</v>
       </c>
       <c r="E10" t="n">
         <v>8.7719</v>
@@ -1708,7 +1724,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6542554463488384</v>
+        <v>0.6542554463488385</v>
       </c>
       <c r="E11" t="n">
         <v>1.768</v>
@@ -1748,7 +1764,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6341203844914751</v>
+        <v>0.6341203844914753</v>
       </c>
       <c r="E13" t="n">
         <v>-1.5267</v>
@@ -1828,7 +1844,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6220923227005735</v>
+        <v>0.6220923227005734</v>
       </c>
       <c r="E17" t="n">
         <v>1.3295</v>
@@ -1888,7 +1904,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6095497587374009</v>
+        <v>0.609549758737401</v>
       </c>
       <c r="E20" t="n">
         <v>-10.5289</v>
@@ -1908,7 +1924,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6057569444292606</v>
+        <v>0.6057569444292608</v>
       </c>
       <c r="E21" t="n">
         <v>4.0638</v>
@@ -1928,7 +1944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1949,25 +1965,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>top_30_return</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>decile_return</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>OMXS30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>OMXC25</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>OMXH25</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>OSEBX</t>
         </is>
@@ -1984,12 +2005,15 @@
         <v>3.22</v>
       </c>
       <c r="D2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E2" t="n">
         <v>-0.87</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2002,12 +2026,15 @@
         <v>2.26</v>
       </c>
       <c r="D3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="E3" t="n">
         <v>2.53</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2020,12 +2047,15 @@
         <v>4.93</v>
       </c>
       <c r="D4" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="E4" t="n">
         <v>2.68</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2038,12 +2068,15 @@
         <v>5.8</v>
       </c>
       <c r="D5" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E5" t="n">
         <v>2.12</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2056,12 +2089,15 @@
         <v>2.06</v>
       </c>
       <c r="D6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E6" t="n">
         <v>2.34</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2074,12 +2110,15 @@
         <v>1.11</v>
       </c>
       <c r="D7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E7" t="n">
         <v>2.18</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2092,12 +2131,15 @@
         <v>4.97</v>
       </c>
       <c r="D8" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="E8" t="n">
         <v>5.32</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2110,12 +2152,15 @@
         <v>3.53</v>
       </c>
       <c r="D9" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E9" t="n">
         <v>2.88</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2128,12 +2173,15 @@
         <v>3.55</v>
       </c>
       <c r="D10" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="E10" t="n">
         <v>3.02</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2418,7 +2466,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6924578263588604</v>
+        <v>0.6924578263588603</v>
       </c>
       <c r="E2" t="n">
         <v>3.4224</v>
@@ -2538,7 +2586,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6682041849984337</v>
+        <v>0.6682041849984336</v>
       </c>
       <c r="E8" t="n">
         <v>1.9081</v>
@@ -2558,7 +2606,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6653880997746329</v>
+        <v>0.6653880997746328</v>
       </c>
       <c r="E9" t="n">
         <v>7.5734</v>
@@ -2658,7 +2706,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6575307276428624</v>
+        <v>0.6575307276428625</v>
       </c>
       <c r="E14" t="n">
         <v>-11.7191</v>
@@ -2738,7 +2786,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.643131125773853</v>
+        <v>0.6431311257738528</v>
       </c>
       <c r="E18" t="n">
         <v>18.2796</v>
@@ -2758,7 +2806,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6389284733394359</v>
+        <v>0.638928473339436</v>
       </c>
       <c r="E19" t="n">
         <v>-0.9804</v>
@@ -2798,7 +2846,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6338642476554566</v>
+        <v>0.6338642476554567</v>
       </c>
       <c r="E21" t="n">
         <v>-2.7554</v>
@@ -2864,7 +2912,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7103095600355903</v>
+        <v>0.7103095600355901</v>
       </c>
       <c r="E2" t="n">
         <v>9.586</v>
@@ -2944,7 +2992,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6884665063664521</v>
+        <v>0.6884665063664522</v>
       </c>
       <c r="E6" t="n">
         <v>1.5243</v>
@@ -2964,7 +3012,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6859495901487074</v>
+        <v>0.6859495901487075</v>
       </c>
       <c r="E7" t="n">
         <v>6.4792</v>
@@ -2984,7 +3032,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6778659197012935</v>
+        <v>0.6778659197012936</v>
       </c>
       <c r="E8" t="n">
         <v>-10.0535</v>
@@ -3004,7 +3052,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6685332154440067</v>
+        <v>0.6685332154440066</v>
       </c>
       <c r="E9" t="n">
         <v>4.8787</v>
@@ -3024,7 +3072,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6673247319361444</v>
+        <v>0.6673247319361443</v>
       </c>
       <c r="E10" t="n">
         <v>1.4271</v>
@@ -3104,7 +3152,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6607784216383287</v>
+        <v>0.6607784216383286</v>
       </c>
       <c r="E14" t="n">
         <v>1.393</v>
@@ -3144,7 +3192,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6535897948763834</v>
+        <v>0.6535897948763835</v>
       </c>
       <c r="E16" t="n">
         <v>0.5142</v>
@@ -3184,7 +3232,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6494139052029061</v>
+        <v>0.649413905202906</v>
       </c>
       <c r="E18" t="n">
         <v>-0.8086</v>
@@ -3204,7 +3252,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6435482600945085</v>
+        <v>0.6435482600945086</v>
       </c>
       <c r="E19" t="n">
         <v>0.1479</v>
@@ -3330,7 +3378,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6771785531731342</v>
+        <v>0.677178553173134</v>
       </c>
       <c r="E3" t="n">
         <v>3.6574</v>
@@ -3350,7 +3398,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.665350201462568</v>
+        <v>0.6653502014625678</v>
       </c>
       <c r="E4" t="n">
         <v>21.179</v>
@@ -3370,7 +3418,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6652973290366911</v>
+        <v>0.665297329036691</v>
       </c>
       <c r="E5" t="n">
         <v>2.6852</v>
@@ -3470,7 +3518,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6533386513346306</v>
+        <v>0.6533386513346305</v>
       </c>
       <c r="E10" t="n">
         <v>8.063000000000001</v>
@@ -3510,7 +3558,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.650378057544182</v>
+        <v>0.6503780575441819</v>
       </c>
       <c r="E12" t="n">
         <v>1.1827</v>
@@ -3570,7 +3618,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6470518803758744</v>
+        <v>0.6470518803758742</v>
       </c>
       <c r="E15" t="n">
         <v>2.8167</v>
@@ -3610,7 +3658,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6435091819735957</v>
+        <v>0.6435091819735956</v>
       </c>
       <c r="E17" t="n">
         <v>1.0049</v>
@@ -3690,7 +3738,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6298809866174913</v>
+        <v>0.6298809866174914</v>
       </c>
       <c r="E21" t="n">
         <v>6.6771</v>
@@ -3776,7 +3824,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7063927518972396</v>
+        <v>0.7063927518972395</v>
       </c>
       <c r="E3" t="n">
         <v>2.1001</v>
@@ -3796,7 +3844,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7029259742932014</v>
+        <v>0.7029259742932013</v>
       </c>
       <c r="E4" t="n">
         <v>6.8729</v>
@@ -3896,7 +3944,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6700409267450809</v>
+        <v>0.670040926745081</v>
       </c>
       <c r="E9" t="n">
         <v>3.3333</v>
@@ -3916,7 +3964,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6643167494060975</v>
+        <v>0.6643167494060974</v>
       </c>
       <c r="E10" t="n">
         <v>1.2021</v>
@@ -3956,7 +4004,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6592919456844157</v>
+        <v>0.6592919456844158</v>
       </c>
       <c r="E12" t="n">
         <v>-2.0284</v>
@@ -3996,7 +4044,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6562052322561766</v>
+        <v>0.6562052322561768</v>
       </c>
       <c r="E14" t="n">
         <v>2.2954</v>
@@ -4036,7 +4084,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6522881664204664</v>
+        <v>0.6522881664204665</v>
       </c>
       <c r="E16" t="n">
         <v>-1.5402</v>
@@ -4076,7 +4124,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6504205845494543</v>
+        <v>0.6504205845494545</v>
       </c>
       <c r="E18" t="n">
         <v>3.0997</v>
@@ -4116,7 +4164,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6449604429442388</v>
+        <v>0.6449604429442387</v>
       </c>
       <c r="E20" t="n">
         <v>7.34</v>
@@ -4222,7 +4270,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7147813875393552</v>
+        <v>0.7147813875393553</v>
       </c>
       <c r="E3" t="n">
         <v>1.2478</v>
@@ -4322,7 +4370,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6674835253781403</v>
+        <v>0.6674835253781404</v>
       </c>
       <c r="E8" t="n">
         <v>0.8485</v>
@@ -4482,7 +4530,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6432809573567764</v>
+        <v>0.6432809573567763</v>
       </c>
       <c r="E16" t="n">
         <v>3.8556</v>
@@ -4542,7 +4590,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6341893776532117</v>
+        <v>0.6341893776532118</v>
       </c>
       <c r="E19" t="n">
         <v>4.7192</v>
@@ -4582,7 +4630,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6309619353381959</v>
+        <v>0.630961935338196</v>
       </c>
       <c r="E21" t="n">
         <v>4.2541</v>
@@ -4648,7 +4696,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7215788478381748</v>
+        <v>0.7215788478381746</v>
       </c>
       <c r="E2" t="n">
         <v>-2.3431</v>
@@ -4708,7 +4756,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.7069295687303945</v>
+        <v>0.7069295687303944</v>
       </c>
       <c r="E5" t="n">
         <v>-4.8858</v>
@@ -4888,7 +4936,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6463005482953201</v>
+        <v>0.64630054829532</v>
       </c>
       <c r="E14" t="n">
         <v>-6.1118</v>
@@ -5008,7 +5056,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.61868170266777</v>
+        <v>0.6186817026677699</v>
       </c>
       <c r="E20" t="n">
         <v>5.4422</v>

--- a/results/reports/year_2019_report.xlsx
+++ b/results/reports/year_2019_report.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6983401854998145</v>
+        <v>0.6983401854998147</v>
       </c>
       <c r="E4" t="n">
         <v>4.1867</v>
@@ -712,7 +712,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6919322411142764</v>
+        <v>0.6919322411142765</v>
       </c>
       <c r="E5" t="n">
         <v>3.1643</v>
@@ -792,7 +792,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6680353861069679</v>
+        <v>0.6680353861069678</v>
       </c>
       <c r="E9" t="n">
         <v>8.0594</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7227837324095772</v>
+        <v>0.7227837324095774</v>
       </c>
       <c r="E2" t="n">
         <v>3.0688</v>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7176547411822642</v>
+        <v>0.7176547411822644</v>
       </c>
       <c r="E3" t="n">
         <v>4.0361</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6939867989200421</v>
+        <v>0.6939867989200422</v>
       </c>
       <c r="E5" t="n">
         <v>-2.9211</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6883931044049939</v>
+        <v>0.6883931044049938</v>
       </c>
       <c r="E6" t="n">
         <v>-3.2609</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6767809593519548</v>
+        <v>0.6767809593519547</v>
       </c>
       <c r="E7" t="n">
         <v>3.7013</v>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6472379873434346</v>
+        <v>0.6472379873434347</v>
       </c>
       <c r="E9" t="n">
         <v>1.6794</v>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6227724604047959</v>
+        <v>0.6227724604047961</v>
       </c>
       <c r="E16" t="n">
         <v>3.5813</v>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6178585763311247</v>
+        <v>0.6178585763311248</v>
       </c>
       <c r="E17" t="n">
         <v>-1.5511</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6171683759875868</v>
+        <v>0.6171683759875869</v>
       </c>
       <c r="E19" t="n">
         <v>11.9243</v>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6684015803418901</v>
+        <v>0.66840158034189</v>
       </c>
       <c r="E8" t="n">
         <v>1.8475</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6610898380587631</v>
+        <v>0.6610898380587633</v>
       </c>
       <c r="E10" t="n">
         <v>8.7719</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6542554463488385</v>
+        <v>0.6542554463488384</v>
       </c>
       <c r="E11" t="n">
         <v>1.768</v>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6481080060981371</v>
+        <v>0.648108006098137</v>
       </c>
       <c r="E12" t="n">
         <v>1.1463</v>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6341203844914753</v>
+        <v>0.6341203844914751</v>
       </c>
       <c r="E13" t="n">
         <v>-1.5267</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6220923227005734</v>
+        <v>0.6220923227005735</v>
       </c>
       <c r="E17" t="n">
         <v>1.3295</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6057569444292608</v>
+        <v>0.6057569444292606</v>
       </c>
       <c r="E21" t="n">
         <v>4.0638</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6924578263588603</v>
+        <v>0.6924578263588604</v>
       </c>
       <c r="E2" t="n">
         <v>3.4224</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6765284169072693</v>
+        <v>0.6765284169072692</v>
       </c>
       <c r="E6" t="n">
         <v>11.5455</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6682041849984336</v>
+        <v>0.6682041849984337</v>
       </c>
       <c r="E8" t="n">
         <v>1.9081</v>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6653880997746328</v>
+        <v>0.6653880997746329</v>
       </c>
       <c r="E9" t="n">
         <v>7.5734</v>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6635900128221199</v>
+        <v>0.66359001282212</v>
       </c>
       <c r="E10" t="n">
         <v>4.705</v>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6582434450357347</v>
+        <v>0.6582434450357346</v>
       </c>
       <c r="E13" t="n">
         <v>14.2171</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6490894752399186</v>
+        <v>0.6490894752399187</v>
       </c>
       <c r="E17" t="n">
         <v>4.1667</v>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6431311257738528</v>
+        <v>0.643131125773853</v>
       </c>
       <c r="E18" t="n">
         <v>18.2796</v>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6859495901487075</v>
+        <v>0.6859495901487074</v>
       </c>
       <c r="E7" t="n">
         <v>6.4792</v>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6778659197012936</v>
+        <v>0.6778659197012935</v>
       </c>
       <c r="E8" t="n">
         <v>-10.0535</v>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6673247319361443</v>
+        <v>0.6673247319361444</v>
       </c>
       <c r="E10" t="n">
         <v>1.4271</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6607784216383286</v>
+        <v>0.6607784216383287</v>
       </c>
       <c r="E14" t="n">
         <v>1.393</v>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6535897948763835</v>
+        <v>0.6535897948763834</v>
       </c>
       <c r="E16" t="n">
         <v>0.5142</v>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.649413905202906</v>
+        <v>0.6494139052029059</v>
       </c>
       <c r="E18" t="n">
         <v>-0.8086</v>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6435482600945086</v>
+        <v>0.6435482600945085</v>
       </c>
       <c r="E19" t="n">
         <v>0.1479</v>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.677178553173134</v>
+        <v>0.6771785531731342</v>
       </c>
       <c r="E3" t="n">
         <v>3.6574</v>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6653502014625678</v>
+        <v>0.665350201462568</v>
       </c>
       <c r="E4" t="n">
         <v>21.179</v>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.665297329036691</v>
+        <v>0.6652973290366911</v>
       </c>
       <c r="E5" t="n">
         <v>2.6852</v>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6533386513346305</v>
+        <v>0.6533386513346306</v>
       </c>
       <c r="E10" t="n">
         <v>8.063000000000001</v>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6470518803758742</v>
+        <v>0.6470518803758744</v>
       </c>
       <c r="E15" t="n">
         <v>2.8167</v>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6435091819735956</v>
+        <v>0.6435091819735957</v>
       </c>
       <c r="E17" t="n">
         <v>1.0049</v>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6328292615325588</v>
+        <v>0.6328292615325587</v>
       </c>
       <c r="E20" t="n">
         <v>8.4381</v>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7029259742932013</v>
+        <v>0.7029259742932014</v>
       </c>
       <c r="E4" t="n">
         <v>6.8729</v>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6643167494060974</v>
+        <v>0.6643167494060975</v>
       </c>
       <c r="E10" t="n">
         <v>1.2021</v>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6592919456844158</v>
+        <v>0.6592919456844157</v>
       </c>
       <c r="E12" t="n">
         <v>-2.0284</v>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6562052322561768</v>
+        <v>0.6562052322561766</v>
       </c>
       <c r="E14" t="n">
         <v>2.2954</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6522881664204665</v>
+        <v>0.6522881664204664</v>
       </c>
       <c r="E16" t="n">
         <v>-1.5402</v>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7147813875393553</v>
+        <v>0.7147813875393552</v>
       </c>
       <c r="E3" t="n">
         <v>1.2478</v>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7056465204561853</v>
+        <v>0.7056465204561855</v>
       </c>
       <c r="E4" t="n">
         <v>6.0409</v>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6805717209709863</v>
+        <v>0.6805717209709864</v>
       </c>
       <c r="E7" t="n">
         <v>8.463200000000001</v>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6674835253781404</v>
+        <v>0.6674835253781403</v>
       </c>
       <c r="E8" t="n">
         <v>0.8485</v>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6611416758589244</v>
+        <v>0.6611416758589241</v>
       </c>
       <c r="E9" t="n">
         <v>9.777799999999999</v>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6602615799506195</v>
+        <v>0.6602615799506196</v>
       </c>
       <c r="E10" t="n">
         <v>-0.3876</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6505805265316268</v>
+        <v>0.6505805265316266</v>
       </c>
       <c r="E14" t="n">
         <v>-0.9524</v>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6432809573567763</v>
+        <v>0.6432809573567764</v>
       </c>
       <c r="E16" t="n">
         <v>3.8556</v>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.638992834242641</v>
+        <v>0.6389928342426411</v>
       </c>
       <c r="E18" t="n">
         <v>-2.7143</v>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6341893776532118</v>
+        <v>0.6341893776532117</v>
       </c>
       <c r="E19" t="n">
         <v>4.7192</v>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.630961935338196</v>
+        <v>0.6309619353381959</v>
       </c>
       <c r="E21" t="n">
         <v>4.2541</v>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7215788478381746</v>
+        <v>0.7215788478381748</v>
       </c>
       <c r="E2" t="n">
         <v>-2.3431</v>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7131390041336109</v>
+        <v>0.7131390041336106</v>
       </c>
       <c r="E4" t="n">
         <v>-5.1763</v>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.7067746649842135</v>
+        <v>0.7067746649842134</v>
       </c>
       <c r="E6" t="n">
         <v>0.6233</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6952466970163066</v>
+        <v>0.6952466970163065</v>
       </c>
       <c r="E8" t="n">
         <v>1.362</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6903914313028575</v>
+        <v>0.6903914313028576</v>
       </c>
       <c r="E9" t="n">
         <v>0.277</v>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6846577418757422</v>
+        <v>0.6846577418757421</v>
       </c>
       <c r="E10" t="n">
         <v>12.5</v>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6523719271888091</v>
+        <v>0.6523719271888089</v>
       </c>
       <c r="E13" t="n">
         <v>0.667</v>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6302543315863731</v>
+        <v>0.630254331586373</v>
       </c>
       <c r="E17" t="n">
         <v>-3.484</v>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6292213023423955</v>
+        <v>0.6292213023423957</v>
       </c>
       <c r="E18" t="n">
         <v>-0.391</v>

--- a/results/reports/year_2019_report.xlsx
+++ b/results/reports/year_2019_report.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6806414917142781</v>
+        <v>0.680641491714278</v>
       </c>
       <c r="E6" t="n">
         <v>1.8459</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6375441412193248</v>
+        <v>0.6375441412193249</v>
       </c>
       <c r="E16" t="n">
         <v>-1.0814</v>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7176547411822644</v>
+        <v>0.7176547411822642</v>
       </c>
       <c r="E3" t="n">
         <v>4.0361</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6483907186864829</v>
+        <v>0.648390718686483</v>
       </c>
       <c r="E8" t="n">
         <v>8.3055</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6328446790753639</v>
+        <v>0.632844679075364</v>
       </c>
       <c r="E11" t="n">
         <v>3.2803</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6271488533785726</v>
+        <v>0.6271488533785725</v>
       </c>
       <c r="E12" t="n">
         <v>-0.9639</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7420425200766954</v>
+        <v>0.7420425200766956</v>
       </c>
       <c r="E2" t="n">
         <v>5.3077</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6959000463485557</v>
+        <v>0.6959000463485556</v>
       </c>
       <c r="E4" t="n">
         <v>7.6678</v>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6861154980586612</v>
+        <v>0.686115498058661</v>
       </c>
       <c r="E6" t="n">
         <v>7.2283</v>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.66840158034189</v>
+        <v>0.6684015803418903</v>
       </c>
       <c r="E8" t="n">
         <v>1.8475</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6610898380587633</v>
+        <v>0.6610898380587632</v>
       </c>
       <c r="E10" t="n">
         <v>8.7719</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6542554463488384</v>
+        <v>0.6542554463488385</v>
       </c>
       <c r="E11" t="n">
         <v>1.768</v>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.648108006098137</v>
+        <v>0.6481080060981371</v>
       </c>
       <c r="E12" t="n">
         <v>1.1463</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.609549758737401</v>
+        <v>0.6095497587374009</v>
       </c>
       <c r="E20" t="n">
         <v>-10.5289</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6924578263588604</v>
+        <v>0.6924578263588601</v>
       </c>
       <c r="E2" t="n">
         <v>3.4224</v>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6830523423474695</v>
+        <v>0.6830523423474696</v>
       </c>
       <c r="E4" t="n">
         <v>9.7059</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6765284169072692</v>
+        <v>0.6765284169072693</v>
       </c>
       <c r="E6" t="n">
         <v>11.5455</v>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.66359001282212</v>
+        <v>0.6635900128221199</v>
       </c>
       <c r="E10" t="n">
         <v>4.705</v>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6582434450357346</v>
+        <v>0.6582434450357347</v>
       </c>
       <c r="E13" t="n">
         <v>14.2171</v>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6575307276428625</v>
+        <v>0.6575307276428624</v>
       </c>
       <c r="E14" t="n">
         <v>-11.7191</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6884665063664522</v>
+        <v>0.6884665063664521</v>
       </c>
       <c r="E6" t="n">
         <v>1.5243</v>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6859495901487074</v>
+        <v>0.6859495901487075</v>
       </c>
       <c r="E7" t="n">
         <v>6.4792</v>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6778659197012935</v>
+        <v>0.6778659197012936</v>
       </c>
       <c r="E8" t="n">
         <v>-10.0535</v>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6673247319361444</v>
+        <v>0.6673247319361443</v>
       </c>
       <c r="E10" t="n">
         <v>1.4271</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6607784216383287</v>
+        <v>0.6607784216383286</v>
       </c>
       <c r="E14" t="n">
         <v>1.393</v>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6535897948763834</v>
+        <v>0.6535897948763835</v>
       </c>
       <c r="E16" t="n">
         <v>0.5142</v>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.651866867056747</v>
+        <v>0.6518668670567471</v>
       </c>
       <c r="E17" t="n">
         <v>4.0173</v>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6494139052029059</v>
+        <v>0.6494139052029061</v>
       </c>
       <c r="E18" t="n">
         <v>-0.8086</v>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.665350201462568</v>
+        <v>0.6653502014625678</v>
       </c>
       <c r="E4" t="n">
         <v>21.179</v>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6652973290366911</v>
+        <v>0.665297329036691</v>
       </c>
       <c r="E5" t="n">
         <v>2.6852</v>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6607443694571041</v>
+        <v>0.660744369457104</v>
       </c>
       <c r="E7" t="n">
         <v>1.7172</v>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6533386513346306</v>
+        <v>0.6533386513346305</v>
       </c>
       <c r="E10" t="n">
         <v>8.063000000000001</v>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6503780575441819</v>
+        <v>0.650378057544182</v>
       </c>
       <c r="E12" t="n">
         <v>1.1827</v>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6470518803758744</v>
+        <v>0.6470518803758742</v>
       </c>
       <c r="E15" t="n">
         <v>2.8167</v>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6435091819735957</v>
+        <v>0.6435091819735956</v>
       </c>
       <c r="E17" t="n">
         <v>1.0049</v>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7063927518972395</v>
+        <v>0.7063927518972396</v>
       </c>
       <c r="E3" t="n">
         <v>2.1001</v>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6822607684033933</v>
+        <v>0.6822607684033934</v>
       </c>
       <c r="E6" t="n">
         <v>7.6421</v>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6708364380425903</v>
+        <v>0.6708364380425904</v>
       </c>
       <c r="E8" t="n">
         <v>-1.2739</v>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.662200641182408</v>
+        <v>0.6622006411824078</v>
       </c>
       <c r="E11" t="n">
         <v>20.9848</v>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6592919456844157</v>
+        <v>0.6592919456844158</v>
       </c>
       <c r="E12" t="n">
         <v>-2.0284</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.657160022726801</v>
+        <v>0.6571600227268009</v>
       </c>
       <c r="E13" t="n">
         <v>10.6875</v>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6529978588623867</v>
+        <v>0.6529978588623865</v>
       </c>
       <c r="E15" t="n">
         <v>8.2089</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6522881664204664</v>
+        <v>0.6522881664204665</v>
       </c>
       <c r="E16" t="n">
         <v>-1.5402</v>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6504205845494545</v>
+        <v>0.6504205845494546</v>
       </c>
       <c r="E18" t="n">
         <v>3.0997</v>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6449604429442387</v>
+        <v>0.6449604429442388</v>
       </c>
       <c r="E20" t="n">
         <v>7.34</v>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7167449142600288</v>
+        <v>0.7167449142600287</v>
       </c>
       <c r="E2" t="n">
         <v>6.4404</v>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7056465204561855</v>
+        <v>0.7056465204561853</v>
       </c>
       <c r="E4" t="n">
         <v>6.0409</v>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.7046542600510806</v>
+        <v>0.7046542600510804</v>
       </c>
       <c r="E5" t="n">
         <v>3.2258</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6505805265316266</v>
+        <v>0.6505805265316268</v>
       </c>
       <c r="E14" t="n">
         <v>-0.9524</v>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6432809573567764</v>
+        <v>0.6432809573567763</v>
       </c>
       <c r="E16" t="n">
         <v>3.8556</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6417781404440618</v>
+        <v>0.6417781404440619</v>
       </c>
       <c r="E17" t="n">
         <v>-2.1023</v>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6389928342426411</v>
+        <v>0.638992834242641</v>
       </c>
       <c r="E18" t="n">
         <v>-2.7143</v>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6309619353381959</v>
+        <v>0.630961935338196</v>
       </c>
       <c r="E21" t="n">
         <v>4.2541</v>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7131390041336106</v>
+        <v>0.7131390041336109</v>
       </c>
       <c r="E4" t="n">
         <v>-5.1763</v>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.7069295687303944</v>
+        <v>0.7069295687303945</v>
       </c>
       <c r="E5" t="n">
         <v>-4.8858</v>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.7067746649842134</v>
+        <v>0.7067746649842135</v>
       </c>
       <c r="E6" t="n">
         <v>0.6233</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6952466970163065</v>
+        <v>0.6952466970163066</v>
       </c>
       <c r="E8" t="n">
         <v>1.362</v>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6846577418757421</v>
+        <v>0.6846577418757422</v>
       </c>
       <c r="E10" t="n">
         <v>12.5</v>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6541734075676015</v>
+        <v>0.6541734075676016</v>
       </c>
       <c r="E12" t="n">
         <v>1.9377</v>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.64630054829532</v>
+        <v>0.6463005482953201</v>
       </c>
       <c r="E14" t="n">
         <v>-6.1118</v>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.630254331586373</v>
+        <v>0.6302543315863731</v>
       </c>
       <c r="E17" t="n">
         <v>-3.484</v>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6292213023423957</v>
+        <v>0.6292213023423955</v>
       </c>
       <c r="E18" t="n">
         <v>-0.391</v>

--- a/results/reports/year_2019_report.xlsx
+++ b/results/reports/year_2019_report.xlsx
@@ -752,7 +752,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6760614234117338</v>
+        <v>0.6760614234117337</v>
       </c>
       <c r="E7" t="n">
         <v>4.6027</v>
@@ -772,7 +772,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6734574236784719</v>
+        <v>0.6734574236784718</v>
       </c>
       <c r="E8" t="n">
         <v>1.3889</v>
@@ -812,7 +812,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6626591061120207</v>
+        <v>0.6626591061120208</v>
       </c>
       <c r="E10" t="n">
         <v>12.093</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6604447862798498</v>
+        <v>0.6604447862798497</v>
       </c>
       <c r="E11" t="n">
         <v>-0.6347</v>
@@ -892,7 +892,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6454815069661904</v>
+        <v>0.6454815069661906</v>
       </c>
       <c r="E14" t="n">
         <v>12.8663</v>
@@ -912,7 +912,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6437598958489474</v>
+        <v>0.6437598958489472</v>
       </c>
       <c r="E15" t="n">
         <v>19.4915</v>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7176547411822642</v>
+        <v>0.7176547411822644</v>
       </c>
       <c r="E3" t="n">
         <v>4.0361</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6883931044049938</v>
+        <v>0.6883931044049936</v>
       </c>
       <c r="E6" t="n">
         <v>-3.2609</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.632844679075364</v>
+        <v>0.6328446790753639</v>
       </c>
       <c r="E11" t="n">
         <v>3.2803</v>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6227724604047961</v>
+        <v>0.6227724604047959</v>
       </c>
       <c r="E16" t="n">
         <v>3.5813</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7420425200766956</v>
+        <v>0.7420425200766952</v>
       </c>
       <c r="E2" t="n">
         <v>5.3077</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7037440193994375</v>
+        <v>0.7037440193994376</v>
       </c>
       <c r="E3" t="n">
         <v>-0.5618</v>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6942264686303387</v>
+        <v>0.6942264686303384</v>
       </c>
       <c r="E5" t="n">
         <v>5.137</v>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6766030916043344</v>
+        <v>0.6766030916043343</v>
       </c>
       <c r="E7" t="n">
         <v>2.4915</v>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6684015803418903</v>
+        <v>0.6684015803418901</v>
       </c>
       <c r="E8" t="n">
         <v>1.8475</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6641355127729556</v>
+        <v>0.6641355127729553</v>
       </c>
       <c r="E9" t="n">
         <v>0.9623</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6610898380587632</v>
+        <v>0.6610898380587631</v>
       </c>
       <c r="E10" t="n">
         <v>8.7719</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6542554463488385</v>
+        <v>0.6542554463488384</v>
       </c>
       <c r="E11" t="n">
         <v>1.768</v>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6253402796784929</v>
+        <v>0.625340279678493</v>
       </c>
       <c r="E16" t="n">
         <v>16.4198</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6057569444292606</v>
+        <v>0.6057569444292605</v>
       </c>
       <c r="E21" t="n">
         <v>4.0638</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6924578263588601</v>
+        <v>0.6924578263588603</v>
       </c>
       <c r="E2" t="n">
         <v>3.4224</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6682041849984337</v>
+        <v>0.6682041849984336</v>
       </c>
       <c r="E8" t="n">
         <v>1.9081</v>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6653880997746329</v>
+        <v>0.6653880997746328</v>
       </c>
       <c r="E9" t="n">
         <v>7.5734</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6600768120903786</v>
+        <v>0.6600768120903784</v>
       </c>
       <c r="E12" t="n">
         <v>-0.09470000000000001</v>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6575307276428624</v>
+        <v>0.6575307276428625</v>
       </c>
       <c r="E14" t="n">
         <v>-11.7191</v>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6549948446932349</v>
+        <v>0.6549948446932348</v>
       </c>
       <c r="E15" t="n">
         <v>-1.8691</v>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.653691598589161</v>
+        <v>0.6536915985891611</v>
       </c>
       <c r="E16" t="n">
         <v>0.2012</v>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.638928473339436</v>
+        <v>0.6389284733394359</v>
       </c>
       <c r="E19" t="n">
         <v>-0.9804</v>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6859495901487075</v>
+        <v>0.6859495901487074</v>
       </c>
       <c r="E7" t="n">
         <v>6.4792</v>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6778659197012936</v>
+        <v>0.6778659197012935</v>
       </c>
       <c r="E8" t="n">
         <v>-10.0535</v>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6518668670567471</v>
+        <v>0.651866867056747</v>
       </c>
       <c r="E17" t="n">
         <v>4.0173</v>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6494139052029061</v>
+        <v>0.649413905202906</v>
       </c>
       <c r="E18" t="n">
         <v>-0.8086</v>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.660744369457104</v>
+        <v>0.6607443694571041</v>
       </c>
       <c r="E7" t="n">
         <v>1.7172</v>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6435091819735956</v>
+        <v>0.6435091819735957</v>
       </c>
       <c r="E17" t="n">
         <v>1.0049</v>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7200378289408195</v>
+        <v>0.7200378289408194</v>
       </c>
       <c r="E2" t="n">
         <v>3.487</v>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7029259742932014</v>
+        <v>0.7029259742932013</v>
       </c>
       <c r="E4" t="n">
         <v>6.8729</v>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6822607684033934</v>
+        <v>0.6822607684033933</v>
       </c>
       <c r="E6" t="n">
         <v>7.6421</v>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6708364380425904</v>
+        <v>0.6708364380425903</v>
       </c>
       <c r="E8" t="n">
         <v>-1.2739</v>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6643167494060975</v>
+        <v>0.6643167494060974</v>
       </c>
       <c r="E10" t="n">
         <v>1.2021</v>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6622006411824078</v>
+        <v>0.662200641182408</v>
       </c>
       <c r="E11" t="n">
         <v>20.9848</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6522881664204665</v>
+        <v>0.6522881664204664</v>
       </c>
       <c r="E16" t="n">
         <v>-1.5402</v>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6504205845494546</v>
+        <v>0.6504205845494545</v>
       </c>
       <c r="E18" t="n">
         <v>3.0997</v>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6449604429442388</v>
+        <v>0.6449604429442387</v>
       </c>
       <c r="E20" t="n">
         <v>7.34</v>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7167449142600287</v>
+        <v>0.7167449142600288</v>
       </c>
       <c r="E2" t="n">
         <v>6.4404</v>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7147813875393552</v>
+        <v>0.7147813875393553</v>
       </c>
       <c r="E3" t="n">
         <v>1.2478</v>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6885527562081887</v>
+        <v>0.6885527562081889</v>
       </c>
       <c r="E6" t="n">
         <v>1.662</v>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6805717209709864</v>
+        <v>0.6805717209709863</v>
       </c>
       <c r="E7" t="n">
         <v>8.463200000000001</v>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6599276303488386</v>
+        <v>0.6599276303488388</v>
       </c>
       <c r="E11" t="n">
         <v>-0.9804</v>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.658622108524285</v>
+        <v>0.6586221085242847</v>
       </c>
       <c r="E12" t="n">
         <v>0.4708</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6505805265316268</v>
+        <v>0.6505805265316266</v>
       </c>
       <c r="E14" t="n">
         <v>-0.9524</v>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6341893776532117</v>
+        <v>0.6341893776532118</v>
       </c>
       <c r="E19" t="n">
         <v>4.7192</v>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.630961935338196</v>
+        <v>0.6309619353381959</v>
       </c>
       <c r="E21" t="n">
         <v>4.2541</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6903914313028576</v>
+        <v>0.6903914313028575</v>
       </c>
       <c r="E9" t="n">
         <v>0.277</v>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6846577418757422</v>
+        <v>0.6846577418757421</v>
       </c>
       <c r="E10" t="n">
         <v>12.5</v>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6541734075676016</v>
+        <v>0.6541734075676015</v>
       </c>
       <c r="E12" t="n">
         <v>1.9377</v>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6463005482953201</v>
+        <v>0.64630054829532</v>
       </c>
       <c r="E14" t="n">
         <v>-6.1118</v>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6302543315863731</v>
+        <v>0.630254331586373</v>
       </c>
       <c r="E17" t="n">
         <v>-3.484</v>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6292213023423955</v>
+        <v>0.6292213023423957</v>
       </c>
       <c r="E18" t="n">
         <v>-0.391</v>
